--- a/data/processed/data_dictionary.xlsx
+++ b/data/processed/data_dictionary.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2016-04-01 to 2016-06-19</t>
+          <t>2016-04-01 to 2016-05-22</t>
         </is>
       </c>
     </row>
